--- a/Avancado/AULA 14 e 15 - TABELA DINÂMICA e FILTROS/2 tabela Dinâmica pág. 79 D.xlsx
+++ b/Avancado/AULA 14 e 15 - TABELA DINÂMICA e FILTROS/2 tabela Dinâmica pág. 79 D.xlsx
@@ -5,18 +5,45 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\AULA 14 e 15 - TABELA DINÂMICA e FILTROS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\AULA 14 e 15 - TABELA DINÂMICA e FILTROS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00DA0AA-8C77-4C09-AD39-AB51C892AC53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5129CFC8-3C85-4A1B-861F-25FC73934DFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DADOS" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="SegmentaçãodeDados_Data_Venda">#N/A</definedName>
+    <definedName name="SegmentaçãodeDados_Depto.">#N/A</definedName>
+    <definedName name="SegmentaçãodeDados_Produto">#N/A</definedName>
+    <definedName name="SegmentaçãodeDados_Qtd">#N/A</definedName>
+    <definedName name="SegmentaçãodeDados_Total">#N/A</definedName>
+    <definedName name="SegmentaçãodeDados_Valor">#N/A</definedName>
+    <definedName name="SegmentaçãodeDados_Vendedor">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="179021"/>
+  <pivotCaches>
+    <pivotCache cacheId="10" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId4"/>
+        <x14:slicerCache r:id="rId5"/>
+        <x14:slicerCache r:id="rId6"/>
+        <x14:slicerCache r:id="rId7"/>
+        <x14:slicerCache r:id="rId8"/>
+        <x14:slicerCache r:id="rId9"/>
+        <x14:slicerCache r:id="rId10"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -25,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="31">
   <si>
     <t>RELATÓRIO DE VENDAS</t>
   </si>
@@ -103,6 +130,21 @@
   </si>
   <si>
     <t>Solange Brandão</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>Vendedores</t>
+  </si>
+  <si>
+    <t>Quantidade</t>
+  </si>
+  <si>
+    <t>Valor total</t>
+  </si>
+  <si>
+    <t>Valor unit.</t>
   </si>
 </sst>
 </file>
@@ -267,7 +309,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -330,12 +372,403 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="136">
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -678,16 +1111,2178 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Vendedor">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEB78212-D8C5-44BA-9D2F-E28AD47958B3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Vendedor"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5305425" y="381000"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Depto.">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7CD1E20-9163-45BA-A832-432E9B793D1C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Depto."/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7153275" y="381000"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Data Venda">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77D46E59-4DC9-4A0C-ACB6-13B27DBA711B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Data Venda"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9010650" y="381000"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="8" name="Produto">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8661A82D-B720-40F2-AEB0-CCA932C84EF5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Produto"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5305425" y="3048000"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="9" name="Valor">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{962372FC-0F63-416A-B43F-B1354E9212C9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Valor"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7153275" y="3048000"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="10" name="Qtd">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A765E592-9935-4F69-9733-8FDA0B2101C6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Qtd"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9010650" y="3048000"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="11" name="Total">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76F2089C-C35E-4540-AD16-E61862953127}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Total"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11096625" y="381000"/>
+              <a:ext cx="1828800" cy="5143500"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="WILCK GOMES DE OLIVEIRA" refreshedDate="46105.81669097222" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="104" xr:uid="{190F27A2-086E-440F-A47B-802A1A377F67}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Tabela1"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="Vendedor" numFmtId="0">
+      <sharedItems count="8">
+        <s v="Ana Maria"/>
+        <s v="André Luiz"/>
+        <s v="Antônio Carlos"/>
+        <s v="Carlos Brandão"/>
+        <s v="João Carlos"/>
+        <s v="José Augusto"/>
+        <s v="Maria Izabel"/>
+        <s v="Solange Brandão"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Depto." numFmtId="0">
+      <sharedItems count="2">
+        <s v="Ótica"/>
+        <s v="Informática"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Data Venda" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2016-07-03T00:00:00" maxDate="2016-12-15T00:00:00" count="28">
+        <d v="2016-08-12T00:00:00"/>
+        <d v="2016-08-15T00:00:00"/>
+        <d v="2016-10-12T00:00:00"/>
+        <d v="2016-11-02T00:00:00"/>
+        <d v="2016-11-10T00:00:00"/>
+        <d v="2016-12-02T00:00:00"/>
+        <d v="2016-12-05T00:00:00"/>
+        <d v="2016-12-11T00:00:00"/>
+        <d v="2016-12-14T00:00:00"/>
+        <d v="2016-07-08T00:00:00"/>
+        <d v="2016-08-07T00:00:00"/>
+        <d v="2016-08-17T00:00:00"/>
+        <d v="2016-10-17T00:00:00"/>
+        <d v="2016-11-07T00:00:00"/>
+        <d v="2016-12-08T00:00:00"/>
+        <d v="2016-07-15T00:00:00"/>
+        <d v="2016-09-05T00:00:00"/>
+        <d v="2016-09-15T00:00:00"/>
+        <d v="2016-08-05T00:00:00"/>
+        <d v="2016-11-06T00:00:00"/>
+        <d v="2016-11-12T00:00:00"/>
+        <d v="2016-07-03T00:00:00"/>
+        <d v="2016-11-09T00:00:00"/>
+        <d v="2016-08-10T00:00:00"/>
+        <d v="2016-11-08T00:00:00"/>
+        <d v="2016-11-05T00:00:00"/>
+        <d v="2016-10-09T00:00:00"/>
+        <d v="2016-11-11T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Produto" numFmtId="0">
+      <sharedItems count="8">
+        <s v="Lente de Contato"/>
+        <s v="Óculos de Sol"/>
+        <s v="Pentium Dual Core"/>
+        <s v="Notebook"/>
+        <s v="Hard Disk 450 Gb"/>
+        <s v="Hard Disk 200 Gb"/>
+        <s v="Pack 10 DVD"/>
+        <s v="Placa de Som"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Valor" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.9" maxValue="2000" count="11">
+        <n v="120"/>
+        <n v="90"/>
+        <n v="150"/>
+        <n v="130"/>
+        <n v="1500"/>
+        <n v="2000"/>
+        <n v="450"/>
+        <n v="335"/>
+        <n v="9.9"/>
+        <n v="467"/>
+        <n v="533"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Qtd" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="6" count="5">
+        <n v="3"/>
+        <n v="2"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Total" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="19.8" maxValue="10000" count="34">
+        <n v="360"/>
+        <n v="270"/>
+        <n v="300"/>
+        <n v="240"/>
+        <n v="520"/>
+        <n v="600"/>
+        <n v="180"/>
+        <n v="650"/>
+        <n v="3000"/>
+        <n v="6000"/>
+        <n v="900"/>
+        <n v="1340"/>
+        <n v="1675"/>
+        <n v="670"/>
+        <n v="1005"/>
+        <n v="260"/>
+        <n v="780"/>
+        <n v="750"/>
+        <n v="450"/>
+        <n v="480"/>
+        <n v="19.8"/>
+        <n v="39.6"/>
+        <n v="1350"/>
+        <n v="1800"/>
+        <n v="29.700000000000003"/>
+        <n v="49.5"/>
+        <n v="1401"/>
+        <n v="1599"/>
+        <n v="2250"/>
+        <n v="1066"/>
+        <n v="390"/>
+        <n v="10000"/>
+        <n v="4000"/>
+        <n v="8000"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="1074951490"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="104">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="2"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="2"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="7"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="7"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="2"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="24"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="24"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="24"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="2"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="2"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="7"/>
+    <x v="10"/>
+    <x v="1"/>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="25"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="25"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="25"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="25"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="25"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="30"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="26"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="2"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="27"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="27"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="27"/>
+    <x v="6"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="27"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="27"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="32"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="33"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E2B4FCD-2BFB-4A6D-8BB9-FC5750525C2E}" name="Tabela dinâmica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Vendedores">
+  <location ref="B3:E38" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="29">
+        <item x="21"/>
+        <item x="9"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="10"/>
+        <item x="23"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="26"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="25"/>
+        <item x="19"/>
+        <item x="13"/>
+        <item x="24"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="27"/>
+        <item x="20"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0">
+      <items count="12">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="44" showAll="0">
+      <items count="35">
+        <item x="20"/>
+        <item x="24"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="30"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item x="29"/>
+        <item x="11"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="28"/>
+        <item x="8"/>
+        <item x="32"/>
+        <item x="9"/>
+        <item x="33"/>
+        <item x="31"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="35">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Quantidade" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Valor unit." fld="4" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="Valor total" fld="6" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="125">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="124">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="105">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2" selected="0">
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Vendedor" xr10:uid="{B8703761-4009-4CFA-B569-0B0E3669884A}" sourceName="Vendedor">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1074951490">
+      <items count="8">
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+        <i x="4" s="1"/>
+        <i x="5" s="1"/>
+        <i x="6" s="1"/>
+        <i x="7" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Depto." xr10:uid="{EC61EC7A-87C2-477C-BAF5-06E32FBB50B1}" sourceName="Depto.">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1074951490">
+      <items count="2">
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Data_Venda" xr10:uid="{0661DADB-6CDA-4C5E-B15C-6AD2639D6742}" sourceName="Data Venda">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1074951490">
+      <items count="28">
+        <i x="21" s="1"/>
+        <i x="9" s="1"/>
+        <i x="15" s="1"/>
+        <i x="18" s="1"/>
+        <i x="10" s="1"/>
+        <i x="23" s="1"/>
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="11" s="1"/>
+        <i x="16" s="1"/>
+        <i x="17" s="1"/>
+        <i x="26" s="1"/>
+        <i x="2" s="1"/>
+        <i x="12" s="1"/>
+        <i x="3" s="1"/>
+        <i x="25" s="1"/>
+        <i x="19" s="1"/>
+        <i x="13" s="1"/>
+        <i x="24" s="1"/>
+        <i x="22" s="1"/>
+        <i x="4" s="1"/>
+        <i x="27" s="1"/>
+        <i x="20" s="1"/>
+        <i x="5" s="1"/>
+        <i x="6" s="1"/>
+        <i x="14" s="1"/>
+        <i x="7" s="1"/>
+        <i x="8" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Produto" xr10:uid="{B0C4B5D8-F12C-41E1-B3F2-4040025B5FDF}" sourceName="Produto">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1074951490">
+      <items count="8">
+        <i x="5" s="1"/>
+        <i x="4" s="1"/>
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+        <i x="1" s="1"/>
+        <i x="6" s="1"/>
+        <i x="2" s="1"/>
+        <i x="7" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache5.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Valor" xr10:uid="{54BE0C76-38ED-4C15-BA2E-8B8FAE3CF3C0}" sourceName="Valor">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1074951490">
+      <items count="11">
+        <i x="8" s="1"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+        <i x="2" s="1"/>
+        <i x="7" s="1"/>
+        <i x="6" s="1"/>
+        <i x="9" s="1"/>
+        <i x="10" s="1"/>
+        <i x="4" s="1"/>
+        <i x="5" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache6.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Qtd" xr10:uid="{8BF9196E-DA9F-4871-872E-880ED4590E58}" sourceName="Qtd">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1074951490">
+      <items count="5">
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+        <i x="4" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache7.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Total" xr10:uid="{8C79F0EF-95B1-4BBF-A382-33DAB2E6B3E4}" sourceName="Total">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1074951490">
+      <items count="34">
+        <i x="20" s="1"/>
+        <i x="24" s="1"/>
+        <i x="21" s="1"/>
+        <i x="25" s="1"/>
+        <i x="6" s="1"/>
+        <i x="3" s="1"/>
+        <i x="15" s="1"/>
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="0" s="1"/>
+        <i x="30" s="1"/>
+        <i x="18" s="1"/>
+        <i x="19" s="1"/>
+        <i x="4" s="1"/>
+        <i x="5" s="1"/>
+        <i x="7" s="1"/>
+        <i x="13" s="1"/>
+        <i x="17" s="1"/>
+        <i x="16" s="1"/>
+        <i x="10" s="1"/>
+        <i x="14" s="1"/>
+        <i x="29" s="1"/>
+        <i x="11" s="1"/>
+        <i x="22" s="1"/>
+        <i x="26" s="1"/>
+        <i x="27" s="1"/>
+        <i x="12" s="1"/>
+        <i x="23" s="1"/>
+        <i x="28" s="1"/>
+        <i x="8" s="1"/>
+        <i x="32" s="1"/>
+        <i x="9" s="1"/>
+        <i x="33" s="1"/>
+        <i x="31" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Vendedor" xr10:uid="{2104E5DC-0BF9-41C2-AE96-1AF757D41C7C}" cache="SegmentaçãodeDados_Vendedor" caption="Vendedor" rowHeight="241300"/>
+  <slicer name="Depto." xr10:uid="{B4F90637-50BD-4432-BD51-4AA4C321A2E3}" cache="SegmentaçãodeDados_Depto." caption="Depto." rowHeight="241300"/>
+  <slicer name="Data Venda" xr10:uid="{53C2348E-99E4-4035-BD0A-1B1078D278D0}" cache="SegmentaçãodeDados_Data_Venda" caption="Data Venda" rowHeight="241300"/>
+  <slicer name="Produto" xr10:uid="{433C1CC3-B255-46AA-A50A-EF8AA736B31F}" cache="SegmentaçãodeDados_Produto" caption="Produto" rowHeight="241300"/>
+  <slicer name="Valor" xr10:uid="{E64D8BE3-3670-400B-8BEC-A1F8355AC5B7}" cache="SegmentaçãodeDados_Valor" caption="Valor" startItem="1" rowHeight="241300"/>
+  <slicer name="Qtd" xr10:uid="{37565677-BB93-4093-B0B0-BC1EF364815A}" cache="SegmentaçãodeDados_Qtd" caption="Qtd" rowHeight="241300"/>
+  <slicer name="Total" xr10:uid="{534A8228-5C04-42AA-86B3-3C3F7ED86891}" cache="SegmentaçãodeDados_Total" caption="Total" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A3:G107" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A3:G107" totalsRowShown="0" headerRowDxfId="135" headerRowBorderDxfId="134" tableBorderDxfId="133">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Vendedor" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Depto." dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Data Venda" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Produto" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Valor" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Qtd" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Total" dataDxfId="0" dataCellStyle="Moeda">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Vendedor" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Depto." dataDxfId="131"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Data Venda" dataDxfId="130"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Produto" dataDxfId="129"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Valor" dataDxfId="128"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Qtd" dataDxfId="127"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Total" dataDxfId="126" dataCellStyle="Moeda">
       <calculatedColumnFormula>E4*F4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3530,4 +6125,547 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E1EB79-DF1B-4495-A6A5-0D5166142BD0}">
+  <dimension ref="B3:E38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="31">
+        <v>41</v>
+      </c>
+      <c r="D4" s="32">
+        <v>1580</v>
+      </c>
+      <c r="E4" s="32">
+        <v>5010</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="31">
+        <v>24</v>
+      </c>
+      <c r="D5" s="32">
+        <v>870</v>
+      </c>
+      <c r="E5" s="32">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="31">
+        <v>17</v>
+      </c>
+      <c r="D6" s="32">
+        <v>710</v>
+      </c>
+      <c r="E6" s="32">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="31">
+        <v>48</v>
+      </c>
+      <c r="D7" s="32">
+        <v>7635</v>
+      </c>
+      <c r="E7" s="32">
+        <v>23635</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="31">
+        <v>41</v>
+      </c>
+      <c r="D8" s="32">
+        <v>3685</v>
+      </c>
+      <c r="E8" s="32">
+        <v>13735</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="31">
+        <v>2</v>
+      </c>
+      <c r="D9" s="32">
+        <v>450</v>
+      </c>
+      <c r="E9" s="32">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="31">
+        <v>3</v>
+      </c>
+      <c r="D10" s="32">
+        <v>2000</v>
+      </c>
+      <c r="E10" s="32">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="31">
+        <v>2</v>
+      </c>
+      <c r="D11" s="32">
+        <v>1500</v>
+      </c>
+      <c r="E11" s="32">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="31">
+        <v>16</v>
+      </c>
+      <c r="D12" s="32">
+        <v>560</v>
+      </c>
+      <c r="E12" s="32">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="31">
+        <v>16</v>
+      </c>
+      <c r="D13" s="32">
+        <v>560</v>
+      </c>
+      <c r="E13" s="32">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="31">
+        <v>72</v>
+      </c>
+      <c r="D14" s="32">
+        <v>3689.6</v>
+      </c>
+      <c r="E14" s="32">
+        <v>11878.8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="31">
+        <v>6</v>
+      </c>
+      <c r="D15" s="32">
+        <v>670</v>
+      </c>
+      <c r="E15" s="32">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="31">
+        <v>9</v>
+      </c>
+      <c r="D16" s="32">
+        <v>1350</v>
+      </c>
+      <c r="E16" s="32">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="31">
+        <v>20</v>
+      </c>
+      <c r="D17" s="32">
+        <v>660</v>
+      </c>
+      <c r="E17" s="32">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="31">
+        <v>25</v>
+      </c>
+      <c r="D18" s="32">
+        <v>970</v>
+      </c>
+      <c r="E18" s="32">
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="31">
+        <v>12</v>
+      </c>
+      <c r="D19" s="32">
+        <v>39.6</v>
+      </c>
+      <c r="E19" s="32">
+        <v>118.80000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="31">
+        <v>45</v>
+      </c>
+      <c r="D20" s="32">
+        <v>3824.9</v>
+      </c>
+      <c r="E20" s="32">
+        <v>12629.5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="31">
+        <v>36</v>
+      </c>
+      <c r="D21" s="32">
+        <v>3685</v>
+      </c>
+      <c r="E21" s="32">
+        <v>12060</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="31">
+        <v>4</v>
+      </c>
+      <c r="D22" s="32">
+        <v>130</v>
+      </c>
+      <c r="E22" s="32">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="31">
+        <v>5</v>
+      </c>
+      <c r="D23" s="32">
+        <v>9.9</v>
+      </c>
+      <c r="E23" s="32">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="31">
+        <v>44</v>
+      </c>
+      <c r="D24" s="32">
+        <v>3927.6</v>
+      </c>
+      <c r="E24" s="32">
+        <v>11749.3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="31">
+        <v>9</v>
+      </c>
+      <c r="D25" s="32">
+        <v>1005</v>
+      </c>
+      <c r="E25" s="32">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="31">
+        <v>10</v>
+      </c>
+      <c r="D26" s="32">
+        <v>1350</v>
+      </c>
+      <c r="E26" s="32">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="31">
+        <v>17</v>
+      </c>
+      <c r="D27" s="32">
+        <v>39.6</v>
+      </c>
+      <c r="E27" s="32">
+        <v>168.3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="31">
+        <v>8</v>
+      </c>
+      <c r="D28" s="32">
+        <v>1533</v>
+      </c>
+      <c r="E28" s="32">
+        <v>4066</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="31">
+        <v>43</v>
+      </c>
+      <c r="D29" s="32">
+        <v>1550</v>
+      </c>
+      <c r="E29" s="32">
+        <v>5110</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="31">
+        <v>31</v>
+      </c>
+      <c r="D30" s="32">
+        <v>990</v>
+      </c>
+      <c r="E30" s="32">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="31">
+        <v>12</v>
+      </c>
+      <c r="D31" s="32">
+        <v>560</v>
+      </c>
+      <c r="E31" s="32">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="31">
+        <v>37</v>
+      </c>
+      <c r="D32" s="32">
+        <v>12324.6</v>
+      </c>
+      <c r="E32" s="32">
+        <v>40239</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="31">
+        <v>4</v>
+      </c>
+      <c r="D33" s="32">
+        <v>335</v>
+      </c>
+      <c r="E33" s="32">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="31">
+        <v>4</v>
+      </c>
+      <c r="D34" s="32">
+        <v>450</v>
+      </c>
+      <c r="E34" s="32">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="31">
+        <v>17</v>
+      </c>
+      <c r="D35" s="32">
+        <v>10000</v>
+      </c>
+      <c r="E35" s="32">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="31">
+        <v>10</v>
+      </c>
+      <c r="D36" s="32">
+        <v>39.6</v>
+      </c>
+      <c r="E36" s="32">
+        <v>99.000000000000014</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="31">
+        <v>2</v>
+      </c>
+      <c r="D37" s="32">
+        <v>1500</v>
+      </c>
+      <c r="E37" s="32">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="31">
+        <v>346</v>
+      </c>
+      <c r="D38" s="32">
+        <v>35091.699999999997</v>
+      </c>
+      <c r="E38" s="32">
+        <v>112491.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
 </file>